--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26531-2026 artfynd.xlsx
+++ b/artfynd/A 26531-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457043</v>
       </c>
       <c r="B2" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
